--- a/outputs/evaluation/requirement/CF_M05_req_eval_by_type.xlsx
+++ b/outputs/evaluation/requirement/CF_M05_req_eval_by_type.xlsx
@@ -535,25 +535,25 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8571</v>
+        <v>0.7143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.75</v>
+        <v>0.7143</v>
       </c>
     </row>
   </sheetData>
